--- a/results/climate_change_breakdown/2050/propanol production, biogas, green ethylene_GLO.xlsx
+++ b/results/climate_change_breakdown/2050/propanol production, biogas, green ethylene_GLO.xlsx
@@ -444,7 +444,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>-1.194793620871306</v>
+        <v>-1.216499546409746</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>-0.5121491655453075</v>
+        <v>-0.5121491655453073</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -478,7 +478,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-0.07924258758665854</v>
+        <v>-0.07924258758665853</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -495,7 +495,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.04406009961770458</v>
+        <v>0.04406009961770459</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-1.172942334421999</v>
+        <v>-1.172942334422</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.02309380232269052</v>
+        <v>0.001470472521877478</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>4.147706284143124E-05</v>
+        <v>1.191373960509171E-06</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>4.404191066691426E-05</v>
+        <v>1.731133496860094E-06</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -580,7 +580,7 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0.001127000340591491</v>
+        <v>0.0011270003405915</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>1.35141562663467E-05</v>
+        <v>1.351415626634692E-05</v>
       </c>
       <c r="E11">
         <v>1</v>
